--- a/output_boron/boron_Intermediate_delavega_2020.xlsx
+++ b/output_boron/boron_Intermediate_delavega_2020.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="374">
   <si>
     <t>NA</t>
   </si>
@@ -1370,13 +1370,16 @@
     <t xml:space="preserve">10.1038/s41598-020-67154-8</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_delavega_2020.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_delavega_2021_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
   </si>
   <si>
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">added age uncertainty based on LR04</t>
   </si>
   <si>
     <t xml:space="preserve">Globigerinoides ruber white</t>
@@ -1768,7 +1771,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1828,12 +1831,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1947,7 +1944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2029,7 +2026,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2636,7 +2632,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2654,8 +2650,8 @@
       <c r="H5" t="n">
         <v>2.34014</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.006</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2663,17 +2659,17 @@
       <c r="K5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L5" t="e">
-        <v>#N/A</v>
+      <c r="L5" t="s">
+        <v>245</v>
       </c>
       <c r="M5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2703,17 +2699,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2731,8 +2727,8 @@
       <c r="H6" t="n">
         <v>2.35085</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.006</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2740,17 +2736,17 @@
       <c r="K6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L6" t="e">
-        <v>#N/A</v>
+      <c r="L6" t="s">
+        <v>245</v>
       </c>
       <c r="M6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2780,17 +2776,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2808,8 +2804,8 @@
       <c r="H7" t="n">
         <v>2.35808</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.006</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2817,17 +2813,17 @@
       <c r="K7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L7" t="e">
-        <v>#N/A</v>
+      <c r="L7" t="s">
+        <v>245</v>
       </c>
       <c r="M7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2857,17 +2853,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2885,8 +2881,8 @@
       <c r="H8" t="n">
         <v>2.37892</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.006</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2894,17 +2890,17 @@
       <c r="K8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L8" t="e">
-        <v>#N/A</v>
+      <c r="L8" t="s">
+        <v>245</v>
       </c>
       <c r="M8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -2934,17 +2930,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2962,8 +2958,8 @@
       <c r="H9" t="n">
         <v>2.38839</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.006</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -2971,17 +2967,17 @@
       <c r="K9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L9" t="e">
-        <v>#N/A</v>
+      <c r="L9" t="s">
+        <v>245</v>
       </c>
       <c r="M9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3011,17 +3007,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -3039,8 +3035,8 @@
       <c r="H10" t="n">
         <v>2.39671</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.006</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3048,17 +3044,17 @@
       <c r="K10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L10" t="e">
-        <v>#N/A</v>
+      <c r="L10" t="s">
+        <v>245</v>
       </c>
       <c r="M10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3088,17 +3084,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -3116,8 +3112,8 @@
       <c r="H11" t="n">
         <v>2.41093</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.006</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3125,17 +3121,17 @@
       <c r="K11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L11" t="e">
-        <v>#N/A</v>
+      <c r="L11" t="s">
+        <v>245</v>
       </c>
       <c r="M11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3165,17 +3161,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -3193,8 +3189,8 @@
       <c r="H12" t="n">
         <v>2.42663</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.006</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3202,17 +3198,17 @@
       <c r="K12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L12" t="e">
-        <v>#N/A</v>
+      <c r="L12" t="s">
+        <v>245</v>
       </c>
       <c r="M12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3242,17 +3238,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3270,8 +3266,8 @@
       <c r="H13" t="n">
         <v>2.45451</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.006</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3279,17 +3275,17 @@
       <c r="K13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L13" t="e">
-        <v>#N/A</v>
+      <c r="L13" t="s">
+        <v>245</v>
       </c>
       <c r="M13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3319,17 +3315,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3347,8 +3343,8 @@
       <c r="H14" t="n">
         <v>2.47382</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.006</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3356,17 +3352,17 @@
       <c r="K14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L14" t="e">
-        <v>#N/A</v>
+      <c r="L14" t="s">
+        <v>245</v>
       </c>
       <c r="M14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3396,17 +3392,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3424,8 +3420,8 @@
       <c r="H15" t="n">
         <v>2.49734</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.006</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3433,17 +3429,17 @@
       <c r="K15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L15" t="e">
-        <v>#N/A</v>
+      <c r="L15" t="s">
+        <v>245</v>
       </c>
       <c r="M15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3473,17 +3469,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3501,8 +3497,8 @@
       <c r="H16" t="n">
         <v>2.4983</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.006</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3510,17 +3506,17 @@
       <c r="K16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L16" t="e">
-        <v>#N/A</v>
+      <c r="L16" t="s">
+        <v>245</v>
       </c>
       <c r="M16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3550,17 +3546,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3578,8 +3574,8 @@
       <c r="H17" t="n">
         <v>2.51716</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.006</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3587,17 +3583,17 @@
       <c r="K17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L17" t="e">
-        <v>#N/A</v>
+      <c r="L17" t="s">
+        <v>245</v>
       </c>
       <c r="M17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -3627,17 +3623,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3655,8 +3651,8 @@
       <c r="H18" t="n">
         <v>2.54044</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.006</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -3664,17 +3660,17 @@
       <c r="K18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L18" t="e">
-        <v>#N/A</v>
+      <c r="L18" t="s">
+        <v>245</v>
       </c>
       <c r="M18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -3704,17 +3700,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3732,8 +3728,8 @@
       <c r="H19" t="n">
         <v>2.5724</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.006</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -3741,17 +3737,17 @@
       <c r="K19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L19" t="e">
-        <v>#N/A</v>
+      <c r="L19" t="s">
+        <v>245</v>
       </c>
       <c r="M19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -3781,17 +3777,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3809,8 +3805,8 @@
       <c r="H20" t="n">
         <v>2.5865</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.006</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -3818,17 +3814,17 @@
       <c r="K20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L20" t="e">
-        <v>#N/A</v>
+      <c r="L20" t="s">
+        <v>245</v>
       </c>
       <c r="M20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -3858,17 +3854,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3886,8 +3882,8 @@
       <c r="H21" t="n">
         <v>2.60034</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.006</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -3895,17 +3891,17 @@
       <c r="K21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L21" t="e">
-        <v>#N/A</v>
+      <c r="L21" t="s">
+        <v>245</v>
       </c>
       <c r="M21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N21" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -3935,17 +3931,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3963,8 +3959,8 @@
       <c r="H22" t="n">
         <v>2.61869</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.006</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -3972,17 +3968,17 @@
       <c r="K22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L22" t="e">
-        <v>#N/A</v>
+      <c r="L22" t="s">
+        <v>245</v>
       </c>
       <c r="M22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4012,17 +4008,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -4040,8 +4036,8 @@
       <c r="H23" t="n">
         <v>2.62686</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.006</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4049,17 +4045,17 @@
       <c r="K23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L23" t="e">
-        <v>#N/A</v>
+      <c r="L23" t="s">
+        <v>245</v>
       </c>
       <c r="M23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4089,17 +4085,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -4117,8 +4113,8 @@
       <c r="H24" t="n">
         <v>2.63274</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.006</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4126,17 +4122,17 @@
       <c r="K24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L24" t="e">
-        <v>#N/A</v>
+      <c r="L24" t="s">
+        <v>245</v>
       </c>
       <c r="M24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4166,17 +4162,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -4194,8 +4190,8 @@
       <c r="H25" t="n">
         <v>2.64736</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.006</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4203,17 +4199,17 @@
       <c r="K25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L25" t="e">
-        <v>#N/A</v>
+      <c r="L25" t="s">
+        <v>245</v>
       </c>
       <c r="M25" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4243,17 +4239,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -4271,8 +4267,8 @@
       <c r="H26" t="n">
         <v>2.66138</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.006</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4280,17 +4276,17 @@
       <c r="K26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L26" t="e">
-        <v>#N/A</v>
+      <c r="L26" t="s">
+        <v>245</v>
       </c>
       <c r="M26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -4320,17 +4316,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4348,8 +4344,8 @@
       <c r="H27" t="n">
         <v>2.67105</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.006</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -4357,17 +4353,17 @@
       <c r="K27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L27" t="e">
-        <v>#N/A</v>
+      <c r="L27" t="s">
+        <v>245</v>
       </c>
       <c r="M27" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N27" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O27" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -4397,17 +4393,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y27" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4425,8 +4421,8 @@
       <c r="H28" t="n">
         <v>2.67921</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.006</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -4434,17 +4430,17 @@
       <c r="K28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L28" t="e">
-        <v>#N/A</v>
+      <c r="L28" t="s">
+        <v>245</v>
       </c>
       <c r="M28" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N28" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O28" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -4474,17 +4470,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y28" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4502,8 +4498,8 @@
       <c r="H29" t="n">
         <v>2.68616</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.006</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -4511,17 +4507,17 @@
       <c r="K29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L29" t="e">
-        <v>#N/A</v>
+      <c r="L29" t="s">
+        <v>245</v>
       </c>
       <c r="M29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N29" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -4551,17 +4547,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4579,8 +4575,8 @@
       <c r="H30" t="n">
         <v>2.69825</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.006</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -4588,17 +4584,17 @@
       <c r="K30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L30" t="e">
-        <v>#N/A</v>
+      <c r="L30" t="s">
+        <v>245</v>
       </c>
       <c r="M30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -4628,17 +4624,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y30" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4656,8 +4652,8 @@
       <c r="H31" t="n">
         <v>2.70551</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.006</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -4665,17 +4661,17 @@
       <c r="K31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L31" t="e">
-        <v>#N/A</v>
+      <c r="L31" t="s">
+        <v>245</v>
       </c>
       <c r="M31" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N31" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O31" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -4705,17 +4701,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4733,8 +4729,8 @@
       <c r="H32" t="n">
         <v>2.71004</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.006</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -4742,17 +4738,17 @@
       <c r="K32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L32" t="e">
-        <v>#N/A</v>
+      <c r="L32" t="s">
+        <v>245</v>
       </c>
       <c r="M32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -4782,17 +4778,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y32" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4810,8 +4806,8 @@
       <c r="H33" t="n">
         <v>2.71609</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.006</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -4819,17 +4815,17 @@
       <c r="K33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L33" t="e">
-        <v>#N/A</v>
+      <c r="L33" t="s">
+        <v>245</v>
       </c>
       <c r="M33" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O33" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -4859,17 +4855,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y33" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4887,8 +4883,8 @@
       <c r="H34" t="n">
         <v>2.74451</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.006</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -4896,17 +4892,17 @@
       <c r="K34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L34" t="e">
-        <v>#N/A</v>
+      <c r="L34" t="s">
+        <v>245</v>
       </c>
       <c r="M34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P34" t="e">
         <v>#N/A</v>
@@ -4936,17 +4932,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y34" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4964,8 +4960,8 @@
       <c r="H35" t="n">
         <v>2.75111</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.006</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -4973,17 +4969,17 @@
       <c r="K35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L35" t="e">
-        <v>#N/A</v>
+      <c r="L35" t="s">
+        <v>245</v>
       </c>
       <c r="M35" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N35" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O35" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -5013,17 +5009,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y35" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s">
         <v>241</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" t="s">
         <v>242</v>
       </c>
       <c r="D36" t="s">
@@ -5041,8 +5037,8 @@
       <c r="H36" t="n">
         <v>2.76459</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.006</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -5050,17 +5046,17 @@
       <c r="K36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L36" t="e">
-        <v>#N/A</v>
+      <c r="L36" t="s">
+        <v>245</v>
       </c>
       <c r="M36" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N36" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O36" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -5090,17 +5086,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" t="s">
         <v>242</v>
       </c>
       <c r="D37" t="s">
@@ -5118,8 +5114,8 @@
       <c r="H37" t="n">
         <v>2.77807</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.006</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -5127,17 +5123,17 @@
       <c r="K37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L37" t="e">
-        <v>#N/A</v>
+      <c r="L37" t="s">
+        <v>245</v>
       </c>
       <c r="M37" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N37" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O37" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P37" t="e">
         <v>#N/A</v>
@@ -5167,17 +5163,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" t="s">
         <v>242</v>
       </c>
       <c r="D38" t="s">
@@ -5195,8 +5191,8 @@
       <c r="H38" t="n">
         <v>2.79952</v>
       </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+      <c r="I38" t="n">
+        <v>0.006</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -5204,17 +5200,17 @@
       <c r="K38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L38" t="e">
-        <v>#N/A</v>
+      <c r="L38" t="s">
+        <v>245</v>
       </c>
       <c r="M38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P38" t="e">
         <v>#N/A</v>
@@ -5244,17 +5240,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" t="s">
         <v>242</v>
       </c>
       <c r="D39" t="s">
@@ -5272,8 +5268,8 @@
       <c r="H39" t="n">
         <v>2.82186</v>
       </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+      <c r="I39" t="n">
+        <v>0.006</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -5281,17 +5277,17 @@
       <c r="K39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L39" t="e">
-        <v>#N/A</v>
+      <c r="L39" t="s">
+        <v>245</v>
       </c>
       <c r="M39" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N39" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O39" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P39" t="e">
         <v>#N/A</v>
@@ -5321,17 +5317,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y39" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s">
         <v>241</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" t="s">
         <v>242</v>
       </c>
       <c r="D40" t="s">
@@ -5349,8 +5345,8 @@
       <c r="H40" t="n">
         <v>2.82345</v>
       </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+      <c r="I40" t="n">
+        <v>0.006</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -5358,17 +5354,17 @@
       <c r="K40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L40" t="e">
-        <v>#N/A</v>
+      <c r="L40" t="s">
+        <v>245</v>
       </c>
       <c r="M40" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N40" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O40" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P40" t="e">
         <v>#N/A</v>
@@ -5398,17 +5394,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y40" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s">
         <v>241</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" t="s">
         <v>242</v>
       </c>
       <c r="D41" t="s">
@@ -5426,8 +5422,8 @@
       <c r="H41" t="n">
         <v>2.83234</v>
       </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+      <c r="I41" t="n">
+        <v>0.006</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -5435,17 +5431,17 @@
       <c r="K41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L41" t="e">
-        <v>#N/A</v>
+      <c r="L41" t="s">
+        <v>245</v>
       </c>
       <c r="M41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N41" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P41" t="e">
         <v>#N/A</v>
@@ -5475,17 +5471,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y41" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B42" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" t="s">
         <v>242</v>
       </c>
       <c r="D42" t="s">
@@ -5503,8 +5499,8 @@
       <c r="H42" t="n">
         <v>2.84505</v>
       </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+      <c r="I42" t="n">
+        <v>0.006</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -5512,17 +5508,17 @@
       <c r="K42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L42" t="e">
-        <v>#N/A</v>
+      <c r="L42" t="s">
+        <v>245</v>
       </c>
       <c r="M42" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O42" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P42" t="e">
         <v>#N/A</v>
@@ -5552,17 +5548,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y42" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B43" t="s">
         <v>241</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" t="s">
         <v>242</v>
       </c>
       <c r="D43" t="s">
@@ -5580,8 +5576,8 @@
       <c r="H43" t="n">
         <v>2.88285</v>
       </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+      <c r="I43" t="n">
+        <v>0.006</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -5589,17 +5585,17 @@
       <c r="K43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L43" t="e">
-        <v>#N/A</v>
+      <c r="L43" t="s">
+        <v>245</v>
       </c>
       <c r="M43" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N43" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O43" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P43" t="e">
         <v>#N/A</v>
@@ -5629,17 +5625,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y43" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B44" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" t="s">
         <v>242</v>
       </c>
       <c r="D44" t="s">
@@ -5657,8 +5653,8 @@
       <c r="H44" t="n">
         <v>2.9162</v>
       </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+      <c r="I44" t="n">
+        <v>0.006</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -5666,17 +5662,17 @@
       <c r="K44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L44" t="e">
-        <v>#N/A</v>
+      <c r="L44" t="s">
+        <v>245</v>
       </c>
       <c r="M44" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N44" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O44" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P44" t="e">
         <v>#N/A</v>
@@ -5706,17 +5702,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y44" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B45" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" t="s">
         <v>242</v>
       </c>
       <c r="D45" t="s">
@@ -5734,8 +5730,8 @@
       <c r="H45" t="n">
         <v>2.927</v>
       </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+      <c r="I45" t="n">
+        <v>0.006</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -5743,17 +5739,17 @@
       <c r="K45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L45" t="e">
-        <v>#N/A</v>
+      <c r="L45" t="s">
+        <v>245</v>
       </c>
       <c r="M45" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P45" t="e">
         <v>#N/A</v>
@@ -5783,17 +5779,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B46" t="s">
         <v>241</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" t="s">
         <v>242</v>
       </c>
       <c r="D46" t="s">
@@ -5811,8 +5807,8 @@
       <c r="H46" t="n">
         <v>2.94297</v>
       </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+      <c r="I46" t="n">
+        <v>0.006</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -5820,17 +5816,17 @@
       <c r="K46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L46" t="e">
-        <v>#N/A</v>
+      <c r="L46" t="s">
+        <v>245</v>
       </c>
       <c r="M46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N46" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P46" t="e">
         <v>#N/A</v>
@@ -5860,17 +5856,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y46" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B47" t="s">
         <v>241</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" t="s">
         <v>242</v>
       </c>
       <c r="D47" t="s">
@@ -5888,8 +5884,8 @@
       <c r="H47" t="n">
         <v>2.95022</v>
       </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+      <c r="I47" t="n">
+        <v>0.006</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -5897,17 +5893,17 @@
       <c r="K47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L47" t="e">
-        <v>#N/A</v>
+      <c r="L47" t="s">
+        <v>245</v>
       </c>
       <c r="M47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N47" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O47" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P47" t="e">
         <v>#N/A</v>
@@ -5937,17 +5933,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B48" t="s">
         <v>241</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" t="s">
         <v>242</v>
       </c>
       <c r="D48" t="s">
@@ -5965,8 +5961,8 @@
       <c r="H48" t="n">
         <v>2.95022</v>
       </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+      <c r="I48" t="n">
+        <v>0.006</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -5974,17 +5970,17 @@
       <c r="K48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L48" t="e">
-        <v>#N/A</v>
+      <c r="L48" t="s">
+        <v>245</v>
       </c>
       <c r="M48" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N48" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P48" t="e">
         <v>#N/A</v>
@@ -6014,17 +6010,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y48" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B49" t="s">
         <v>241</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" t="s">
         <v>242</v>
       </c>
       <c r="D49" t="s">
@@ -6042,8 +6038,8 @@
       <c r="H49" t="n">
         <v>2.95669</v>
       </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+      <c r="I49" t="n">
+        <v>0.006</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -6051,17 +6047,17 @@
       <c r="K49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L49" t="e">
-        <v>#N/A</v>
+      <c r="L49" t="s">
+        <v>245</v>
       </c>
       <c r="M49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P49" t="e">
         <v>#N/A</v>
@@ -6091,17 +6087,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B50" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" t="s">
         <v>242</v>
       </c>
       <c r="D50" t="s">
@@ -6119,8 +6115,8 @@
       <c r="H50" t="n">
         <v>2.9717</v>
       </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+      <c r="I50" t="n">
+        <v>0.006</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -6128,17 +6124,17 @@
       <c r="K50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L50" t="e">
-        <v>#N/A</v>
+      <c r="L50" t="s">
+        <v>245</v>
       </c>
       <c r="M50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P50" t="e">
         <v>#N/A</v>
@@ -6168,17 +6164,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B51" t="s">
         <v>241</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" t="s">
         <v>242</v>
       </c>
       <c r="D51" t="s">
@@ -6196,8 +6192,8 @@
       <c r="H51" t="n">
         <v>2.99811</v>
       </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+      <c r="I51" t="n">
+        <v>0.006</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -6205,17 +6201,17 @@
       <c r="K51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L51" t="e">
-        <v>#N/A</v>
+      <c r="L51" t="s">
+        <v>245</v>
       </c>
       <c r="M51" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P51" t="e">
         <v>#N/A</v>
@@ -6245,17 +6241,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y51" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B52" t="s">
         <v>241</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" t="s">
         <v>242</v>
       </c>
       <c r="D52" t="s">
@@ -6273,8 +6269,8 @@
       <c r="H52" t="n">
         <v>3.00665</v>
       </c>
-      <c r="I52" t="e">
-        <v>#N/A</v>
+      <c r="I52" t="n">
+        <v>0.015</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -6282,17 +6278,17 @@
       <c r="K52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L52" t="e">
-        <v>#N/A</v>
+      <c r="L52" t="s">
+        <v>245</v>
       </c>
       <c r="M52" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P52" t="e">
         <v>#N/A</v>
@@ -6322,17 +6318,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B53" t="s">
         <v>241</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" t="s">
         <v>242</v>
       </c>
       <c r="D53" t="s">
@@ -6350,8 +6346,8 @@
       <c r="H53" t="n">
         <v>3.02322</v>
       </c>
-      <c r="I53" t="e">
-        <v>#N/A</v>
+      <c r="I53" t="n">
+        <v>0.015</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -6359,17 +6355,17 @@
       <c r="K53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L53" t="e">
-        <v>#N/A</v>
+      <c r="L53" t="s">
+        <v>245</v>
       </c>
       <c r="M53" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N53" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O53" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P53" t="e">
         <v>#N/A</v>
@@ -6399,17 +6395,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y53" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B54" t="s">
         <v>241</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" t="s">
         <v>242</v>
       </c>
       <c r="D54" t="s">
@@ -6427,8 +6423,8 @@
       <c r="H54" t="n">
         <v>3.04193</v>
       </c>
-      <c r="I54" t="e">
-        <v>#N/A</v>
+      <c r="I54" t="n">
+        <v>0.015</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -6436,17 +6432,17 @@
       <c r="K54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L54" t="e">
-        <v>#N/A</v>
+      <c r="L54" t="s">
+        <v>245</v>
       </c>
       <c r="M54" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N54" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P54" t="e">
         <v>#N/A</v>
@@ -6476,17 +6472,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B55" t="s">
         <v>241</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" t="s">
         <v>242</v>
       </c>
       <c r="D55" t="s">
@@ -6504,8 +6500,8 @@
       <c r="H55" t="n">
         <v>3.05127</v>
       </c>
-      <c r="I55" t="e">
-        <v>#N/A</v>
+      <c r="I55" t="n">
+        <v>0.015</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -6513,17 +6509,17 @@
       <c r="K55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L55" t="e">
-        <v>#N/A</v>
+      <c r="L55" t="s">
+        <v>245</v>
       </c>
       <c r="M55" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N55" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O55" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P55" t="e">
         <v>#N/A</v>
@@ -6553,17 +6549,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y55" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B56" t="s">
         <v>241</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" t="s">
         <v>242</v>
       </c>
       <c r="D56" t="s">
@@ -6581,8 +6577,8 @@
       <c r="H56" t="n">
         <v>3.0608</v>
       </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+      <c r="I56" t="n">
+        <v>0.015</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -6590,17 +6586,17 @@
       <c r="K56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L56" t="e">
-        <v>#N/A</v>
+      <c r="L56" t="s">
+        <v>245</v>
       </c>
       <c r="M56" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N56" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P56" t="e">
         <v>#N/A</v>
@@ -6630,17 +6626,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y56" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B57" t="s">
         <v>241</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" t="s">
         <v>242</v>
       </c>
       <c r="D57" t="s">
@@ -6658,8 +6654,8 @@
       <c r="H57" t="n">
         <v>3.06467</v>
       </c>
-      <c r="I57" t="e">
-        <v>#N/A</v>
+      <c r="I57" t="n">
+        <v>0.015</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -6667,17 +6663,17 @@
       <c r="K57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L57" t="e">
-        <v>#N/A</v>
+      <c r="L57" t="s">
+        <v>245</v>
       </c>
       <c r="M57" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N57" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O57" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P57" t="e">
         <v>#N/A</v>
@@ -6707,17 +6703,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y57" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B58" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" t="s">
         <v>242</v>
       </c>
       <c r="D58" t="s">
@@ -6735,8 +6731,8 @@
       <c r="H58" t="n">
         <v>3.06799</v>
       </c>
-      <c r="I58" t="e">
-        <v>#N/A</v>
+      <c r="I58" t="n">
+        <v>0.015</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -6744,17 +6740,17 @@
       <c r="K58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L58" t="e">
-        <v>#N/A</v>
+      <c r="L58" t="s">
+        <v>245</v>
       </c>
       <c r="M58" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N58" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O58" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P58" t="e">
         <v>#N/A</v>
@@ -6784,17 +6780,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y58" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B59" t="s">
         <v>241</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" t="s">
         <v>242</v>
       </c>
       <c r="D59" t="s">
@@ -6812,8 +6808,8 @@
       <c r="H59" t="n">
         <v>3.0912</v>
       </c>
-      <c r="I59" t="e">
-        <v>#N/A</v>
+      <c r="I59" t="n">
+        <v>0.015</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -6821,17 +6817,17 @@
       <c r="K59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L59" t="e">
-        <v>#N/A</v>
+      <c r="L59" t="s">
+        <v>245</v>
       </c>
       <c r="M59" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N59" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O59" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P59" t="e">
         <v>#N/A</v>
@@ -6861,17 +6857,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y59" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B60" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" t="s">
         <v>242</v>
       </c>
       <c r="D60" t="s">
@@ -6889,8 +6885,8 @@
       <c r="H60" t="n">
         <v>3.09949</v>
       </c>
-      <c r="I60" t="e">
-        <v>#N/A</v>
+      <c r="I60" t="n">
+        <v>0.015</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -6898,17 +6894,17 @@
       <c r="K60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L60" t="e">
-        <v>#N/A</v>
+      <c r="L60" t="s">
+        <v>245</v>
       </c>
       <c r="M60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N60" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O60" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P60" t="e">
         <v>#N/A</v>
@@ -6938,17 +6934,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y60" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B61" t="s">
         <v>241</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" t="s">
         <v>242</v>
       </c>
       <c r="D61" t="s">
@@ -6966,8 +6962,8 @@
       <c r="H61" t="n">
         <v>3.1122</v>
       </c>
-      <c r="I61" t="e">
-        <v>#N/A</v>
+      <c r="I61" t="n">
+        <v>0.015</v>
       </c>
       <c r="J61" t="e">
         <v>#N/A</v>
@@ -6975,17 +6971,17 @@
       <c r="K61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L61" t="e">
-        <v>#N/A</v>
+      <c r="L61" t="s">
+        <v>245</v>
       </c>
       <c r="M61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O61" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P61" t="e">
         <v>#N/A</v>
@@ -7015,17 +7011,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y61" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B62" t="s">
         <v>241</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" t="s">
         <v>242</v>
       </c>
       <c r="D62" t="s">
@@ -7043,8 +7039,8 @@
       <c r="H62" t="n">
         <v>3.13459</v>
       </c>
-      <c r="I62" t="e">
-        <v>#N/A</v>
+      <c r="I62" t="n">
+        <v>0.015</v>
       </c>
       <c r="J62" t="e">
         <v>#N/A</v>
@@ -7052,17 +7048,17 @@
       <c r="K62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L62" t="e">
-        <v>#N/A</v>
+      <c r="L62" t="s">
+        <v>245</v>
       </c>
       <c r="M62" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N62" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O62" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P62" t="e">
         <v>#N/A</v>
@@ -7092,17 +7088,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y62" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B63" t="s">
         <v>241</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" t="s">
         <v>242</v>
       </c>
       <c r="D63" t="s">
@@ -7120,8 +7116,8 @@
       <c r="H63" t="n">
         <v>3.14671</v>
       </c>
-      <c r="I63" t="e">
-        <v>#N/A</v>
+      <c r="I63" t="n">
+        <v>0.015</v>
       </c>
       <c r="J63" t="e">
         <v>#N/A</v>
@@ -7129,17 +7125,17 @@
       <c r="K63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L63" t="e">
-        <v>#N/A</v>
+      <c r="L63" t="s">
+        <v>245</v>
       </c>
       <c r="M63" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O63" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P63" t="e">
         <v>#N/A</v>
@@ -7169,17 +7165,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y63" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
       <c r="A64" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B64" t="s">
         <v>241</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" t="s">
         <v>242</v>
       </c>
       <c r="D64" t="s">
@@ -7197,8 +7193,8 @@
       <c r="H64" t="n">
         <v>3.1498</v>
       </c>
-      <c r="I64" t="e">
-        <v>#N/A</v>
+      <c r="I64" t="n">
+        <v>0.015</v>
       </c>
       <c r="J64" t="e">
         <v>#N/A</v>
@@ -7206,17 +7202,17 @@
       <c r="K64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L64" t="e">
-        <v>#N/A</v>
+      <c r="L64" t="s">
+        <v>245</v>
       </c>
       <c r="M64" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N64" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P64" t="e">
         <v>#N/A</v>
@@ -7246,17 +7242,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y64" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
       <c r="A65" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B65" t="s">
         <v>241</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" t="s">
         <v>242</v>
       </c>
       <c r="D65" t="s">
@@ -7274,8 +7270,8 @@
       <c r="H65" t="n">
         <v>3.15175</v>
       </c>
-      <c r="I65" t="e">
-        <v>#N/A</v>
+      <c r="I65" t="n">
+        <v>0.015</v>
       </c>
       <c r="J65" t="e">
         <v>#N/A</v>
@@ -7283,17 +7279,17 @@
       <c r="K65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L65" t="e">
-        <v>#N/A</v>
+      <c r="L65" t="s">
+        <v>245</v>
       </c>
       <c r="M65" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N65" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O65" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P65" t="e">
         <v>#N/A</v>
@@ -7323,17 +7319,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y65" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
       <c r="A66" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B66" t="s">
         <v>241</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" t="s">
         <v>242</v>
       </c>
       <c r="D66" t="s">
@@ -7351,8 +7347,8 @@
       <c r="H66" t="n">
         <v>3.15224</v>
       </c>
-      <c r="I66" t="e">
-        <v>#N/A</v>
+      <c r="I66" t="n">
+        <v>0.015</v>
       </c>
       <c r="J66" t="e">
         <v>#N/A</v>
@@ -7360,17 +7356,17 @@
       <c r="K66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L66" t="e">
-        <v>#N/A</v>
+      <c r="L66" t="s">
+        <v>245</v>
       </c>
       <c r="M66" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N66" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P66" t="e">
         <v>#N/A</v>
@@ -7400,17 +7396,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y66" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
       <c r="A67" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B67" t="s">
         <v>241</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" t="s">
         <v>242</v>
       </c>
       <c r="D67" t="s">
@@ -7428,8 +7424,8 @@
       <c r="H67" t="n">
         <v>3.15305</v>
       </c>
-      <c r="I67" t="e">
-        <v>#N/A</v>
+      <c r="I67" t="n">
+        <v>0.015</v>
       </c>
       <c r="J67" t="e">
         <v>#N/A</v>
@@ -7437,17 +7433,17 @@
       <c r="K67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L67" t="e">
-        <v>#N/A</v>
+      <c r="L67" t="s">
+        <v>245</v>
       </c>
       <c r="M67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N67" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O67" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P67" t="e">
         <v>#N/A</v>
@@ -7477,17 +7473,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
       <c r="A68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B68" t="s">
         <v>241</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" t="s">
         <v>242</v>
       </c>
       <c r="D68" t="s">
@@ -7505,8 +7501,8 @@
       <c r="H68" t="n">
         <v>3.15435</v>
       </c>
-      <c r="I68" t="e">
-        <v>#N/A</v>
+      <c r="I68" t="n">
+        <v>0.015</v>
       </c>
       <c r="J68" t="e">
         <v>#N/A</v>
@@ -7514,17 +7510,17 @@
       <c r="K68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L68" t="e">
-        <v>#N/A</v>
+      <c r="L68" t="s">
+        <v>245</v>
       </c>
       <c r="M68" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P68" t="e">
         <v>#N/A</v>
@@ -7554,17 +7550,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
       <c r="A69" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B69" t="s">
         <v>241</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" t="s">
         <v>242</v>
       </c>
       <c r="D69" t="s">
@@ -7582,8 +7578,8 @@
       <c r="H69" t="n">
         <v>3.15533</v>
       </c>
-      <c r="I69" t="e">
-        <v>#N/A</v>
+      <c r="I69" t="n">
+        <v>0.015</v>
       </c>
       <c r="J69" t="e">
         <v>#N/A</v>
@@ -7591,17 +7587,17 @@
       <c r="K69" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L69" t="e">
-        <v>#N/A</v>
+      <c r="L69" t="s">
+        <v>245</v>
       </c>
       <c r="M69" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N69" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O69" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P69" t="e">
         <v>#N/A</v>
@@ -7631,17 +7627,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y69" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
       <c r="A70" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B70" t="s">
         <v>241</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" t="s">
         <v>242</v>
       </c>
       <c r="D70" t="s">
@@ -7659,8 +7655,8 @@
       <c r="H70" t="n">
         <v>3.1568</v>
       </c>
-      <c r="I70" t="e">
-        <v>#N/A</v>
+      <c r="I70" t="n">
+        <v>0.015</v>
       </c>
       <c r="J70" t="e">
         <v>#N/A</v>
@@ -7668,17 +7664,17 @@
       <c r="K70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L70" t="e">
-        <v>#N/A</v>
+      <c r="L70" t="s">
+        <v>245</v>
       </c>
       <c r="M70" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N70" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O70" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P70" t="e">
         <v>#N/A</v>
@@ -7708,17 +7704,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y70" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
       <c r="A71" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B71" t="s">
         <v>241</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" t="s">
         <v>242</v>
       </c>
       <c r="D71" t="s">
@@ -7736,8 +7732,8 @@
       <c r="H71" t="n">
         <v>3.15875</v>
       </c>
-      <c r="I71" t="e">
-        <v>#N/A</v>
+      <c r="I71" t="n">
+        <v>0.015</v>
       </c>
       <c r="J71" t="e">
         <v>#N/A</v>
@@ -7745,17 +7741,17 @@
       <c r="K71" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L71" t="e">
-        <v>#N/A</v>
+      <c r="L71" t="s">
+        <v>245</v>
       </c>
       <c r="M71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N71" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O71" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P71" t="e">
         <v>#N/A</v>
@@ -7785,17 +7781,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y71" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
       <c r="A72" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B72" t="s">
         <v>241</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" t="s">
         <v>242</v>
       </c>
       <c r="D72" t="s">
@@ -7813,8 +7809,8 @@
       <c r="H72" t="n">
         <v>3.16005</v>
       </c>
-      <c r="I72" t="e">
-        <v>#N/A</v>
+      <c r="I72" t="n">
+        <v>0.015</v>
       </c>
       <c r="J72" t="e">
         <v>#N/A</v>
@@ -7822,17 +7818,17 @@
       <c r="K72" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L72" t="e">
-        <v>#N/A</v>
+      <c r="L72" t="s">
+        <v>245</v>
       </c>
       <c r="M72" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O72" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P72" t="e">
         <v>#N/A</v>
@@ -7862,17 +7858,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73" ht="19" customHeight="1">
       <c r="A73" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B73" t="s">
         <v>241</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" t="s">
         <v>242</v>
       </c>
       <c r="D73" t="s">
@@ -7890,8 +7886,8 @@
       <c r="H73" t="n">
         <v>3.16038</v>
       </c>
-      <c r="I73" t="e">
-        <v>#N/A</v>
+      <c r="I73" t="n">
+        <v>0.015</v>
       </c>
       <c r="J73" t="e">
         <v>#N/A</v>
@@ -7899,17 +7895,17 @@
       <c r="K73" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L73" t="e">
-        <v>#N/A</v>
+      <c r="L73" t="s">
+        <v>245</v>
       </c>
       <c r="M73" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N73" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P73" t="e">
         <v>#N/A</v>
@@ -7939,17 +7935,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" ht="19" customHeight="1">
       <c r="A74" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B74" t="s">
         <v>241</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" t="s">
         <v>242</v>
       </c>
       <c r="D74" t="s">
@@ -7967,8 +7963,8 @@
       <c r="H74" t="n">
         <v>3.16192</v>
       </c>
-      <c r="I74" t="e">
-        <v>#N/A</v>
+      <c r="I74" t="n">
+        <v>0.015</v>
       </c>
       <c r="J74" t="e">
         <v>#N/A</v>
@@ -7976,17 +7972,17 @@
       <c r="K74" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L74" t="e">
-        <v>#N/A</v>
+      <c r="L74" t="s">
+        <v>245</v>
       </c>
       <c r="M74" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N74" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O74" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P74" t="e">
         <v>#N/A</v>
@@ -8016,17 +8012,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y74" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
       <c r="A75" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B75" t="s">
         <v>241</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" t="s">
         <v>242</v>
       </c>
       <c r="D75" t="s">
@@ -8044,8 +8040,8 @@
       <c r="H75" t="n">
         <v>3.16314</v>
       </c>
-      <c r="I75" t="e">
-        <v>#N/A</v>
+      <c r="I75" t="n">
+        <v>0.015</v>
       </c>
       <c r="J75" t="e">
         <v>#N/A</v>
@@ -8053,17 +8049,17 @@
       <c r="K75" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L75" t="e">
-        <v>#N/A</v>
+      <c r="L75" t="s">
+        <v>245</v>
       </c>
       <c r="M75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P75" t="e">
         <v>#N/A</v>
@@ -8093,17 +8089,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y75" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
       <c r="A76" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B76" t="s">
         <v>241</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" t="s">
         <v>242</v>
       </c>
       <c r="D76" t="s">
@@ -8121,8 +8117,8 @@
       <c r="H76" t="n">
         <v>3.17665</v>
       </c>
-      <c r="I76" t="e">
-        <v>#N/A</v>
+      <c r="I76" t="n">
+        <v>0.015</v>
       </c>
       <c r="J76" t="e">
         <v>#N/A</v>
@@ -8130,17 +8126,17 @@
       <c r="K76" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L76" t="e">
-        <v>#N/A</v>
+      <c r="L76" t="s">
+        <v>245</v>
       </c>
       <c r="M76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P76" t="e">
         <v>#N/A</v>
@@ -8170,17 +8166,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" ht="19" customHeight="1">
       <c r="A77" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B77" t="s">
         <v>241</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" t="s">
         <v>242</v>
       </c>
       <c r="D77" t="s">
@@ -8198,8 +8194,8 @@
       <c r="H77" t="n">
         <v>3.18088</v>
       </c>
-      <c r="I77" t="e">
-        <v>#N/A</v>
+      <c r="I77" t="n">
+        <v>0.015</v>
       </c>
       <c r="J77" t="e">
         <v>#N/A</v>
@@ -8207,17 +8203,17 @@
       <c r="K77" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L77" t="e">
-        <v>#N/A</v>
+      <c r="L77" t="s">
+        <v>245</v>
       </c>
       <c r="M77" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" t="e">
         <v>#N/A</v>
@@ -8247,17 +8243,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
       <c r="A78" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B78" t="s">
         <v>241</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" t="s">
         <v>242</v>
       </c>
       <c r="D78" t="s">
@@ -8275,8 +8271,8 @@
       <c r="H78" t="n">
         <v>3.18153</v>
       </c>
-      <c r="I78" t="e">
-        <v>#N/A</v>
+      <c r="I78" t="n">
+        <v>0.015</v>
       </c>
       <c r="J78" t="e">
         <v>#N/A</v>
@@ -8284,17 +8280,17 @@
       <c r="K78" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L78" t="e">
-        <v>#N/A</v>
+      <c r="L78" t="s">
+        <v>245</v>
       </c>
       <c r="M78" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N78" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P78" t="e">
         <v>#N/A</v>
@@ -8324,17 +8320,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y78" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1">
       <c r="A79" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B79" t="s">
         <v>241</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" t="s">
         <v>242</v>
       </c>
       <c r="D79" t="s">
@@ -8352,8 +8348,8 @@
       <c r="H79" t="n">
         <v>3.18478</v>
       </c>
-      <c r="I79" t="e">
-        <v>#N/A</v>
+      <c r="I79" t="n">
+        <v>0.015</v>
       </c>
       <c r="J79" t="e">
         <v>#N/A</v>
@@ -8361,17 +8357,17 @@
       <c r="K79" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L79" t="e">
-        <v>#N/A</v>
+      <c r="L79" t="s">
+        <v>245</v>
       </c>
       <c r="M79" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N79" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O79" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P79" t="e">
         <v>#N/A</v>
@@ -8401,17 +8397,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y79" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="80" ht="19" customHeight="1">
       <c r="A80" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B80" t="s">
         <v>241</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" t="s">
         <v>242</v>
       </c>
       <c r="D80" t="s">
@@ -8429,8 +8425,8 @@
       <c r="H80" t="n">
         <v>3.18527</v>
       </c>
-      <c r="I80" t="e">
-        <v>#N/A</v>
+      <c r="I80" t="n">
+        <v>0.015</v>
       </c>
       <c r="J80" t="e">
         <v>#N/A</v>
@@ -8438,17 +8434,17 @@
       <c r="K80" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L80" t="e">
-        <v>#N/A</v>
+      <c r="L80" t="s">
+        <v>245</v>
       </c>
       <c r="M80" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N80" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O80" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P80" t="e">
         <v>#N/A</v>
@@ -8478,17 +8474,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y80" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
       <c r="A81" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B81" t="s">
         <v>241</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" t="s">
         <v>242</v>
       </c>
       <c r="D81" t="s">
@@ -8506,8 +8502,8 @@
       <c r="H81" t="n">
         <v>3.18641</v>
       </c>
-      <c r="I81" t="e">
-        <v>#N/A</v>
+      <c r="I81" t="n">
+        <v>0.015</v>
       </c>
       <c r="J81" t="e">
         <v>#N/A</v>
@@ -8515,17 +8511,17 @@
       <c r="K81" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L81" t="e">
-        <v>#N/A</v>
+      <c r="L81" t="s">
+        <v>245</v>
       </c>
       <c r="M81" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N81" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P81" t="e">
         <v>#N/A</v>
@@ -8555,17 +8551,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y81" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
       <c r="A82" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B82" t="s">
         <v>241</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" t="s">
         <v>242</v>
       </c>
       <c r="D82" t="s">
@@ -8583,8 +8579,8 @@
       <c r="H82" t="n">
         <v>3.19083</v>
       </c>
-      <c r="I82" t="e">
-        <v>#N/A</v>
+      <c r="I82" t="n">
+        <v>0.015</v>
       </c>
       <c r="J82" t="e">
         <v>#N/A</v>
@@ -8592,17 +8588,17 @@
       <c r="K82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L82" t="e">
-        <v>#N/A</v>
+      <c r="L82" t="s">
+        <v>245</v>
       </c>
       <c r="M82" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N82" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O82" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P82" t="e">
         <v>#N/A</v>
@@ -8632,17 +8628,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y82" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="83" ht="19" customHeight="1">
       <c r="A83" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B83" t="s">
         <v>241</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" t="s">
         <v>242</v>
       </c>
       <c r="D83" t="s">
@@ -8660,8 +8656,8 @@
       <c r="H83" t="n">
         <v>3.19203</v>
       </c>
-      <c r="I83" t="e">
-        <v>#N/A</v>
+      <c r="I83" t="n">
+        <v>0.015</v>
       </c>
       <c r="J83" t="e">
         <v>#N/A</v>
@@ -8669,17 +8665,17 @@
       <c r="K83" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L83" t="e">
-        <v>#N/A</v>
+      <c r="L83" t="s">
+        <v>245</v>
       </c>
       <c r="M83" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N83" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O83" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P83" t="e">
         <v>#N/A</v>
@@ -8709,17 +8705,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y83" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="84" ht="19" customHeight="1">
       <c r="A84" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B84" t="s">
         <v>241</v>
       </c>
-      <c r="C84" s="29" t="s">
+      <c r="C84" t="s">
         <v>242</v>
       </c>
       <c r="D84" t="s">
@@ -8737,8 +8733,8 @@
       <c r="H84" t="n">
         <v>3.19595</v>
       </c>
-      <c r="I84" t="e">
-        <v>#N/A</v>
+      <c r="I84" t="n">
+        <v>0.015</v>
       </c>
       <c r="J84" t="e">
         <v>#N/A</v>
@@ -8746,17 +8742,17 @@
       <c r="K84" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L84" t="e">
-        <v>#N/A</v>
+      <c r="L84" t="s">
+        <v>245</v>
       </c>
       <c r="M84" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N84" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O84" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P84" t="e">
         <v>#N/A</v>
@@ -8786,17 +8782,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y84" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="85" ht="19" customHeight="1">
       <c r="A85" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B85" t="s">
         <v>241</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" t="s">
         <v>242</v>
       </c>
       <c r="D85" t="s">
@@ -8814,8 +8810,8 @@
       <c r="H85" t="n">
         <v>3.20288</v>
       </c>
-      <c r="I85" t="e">
-        <v>#N/A</v>
+      <c r="I85" t="n">
+        <v>0.015</v>
       </c>
       <c r="J85" t="e">
         <v>#N/A</v>
@@ -8823,17 +8819,17 @@
       <c r="K85" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L85" t="e">
-        <v>#N/A</v>
+      <c r="L85" t="s">
+        <v>245</v>
       </c>
       <c r="M85" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N85" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O85" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P85" t="e">
         <v>#N/A</v>
@@ -8863,17 +8859,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y85" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" ht="19" customHeight="1">
       <c r="A86" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B86" t="s">
         <v>241</v>
       </c>
-      <c r="C86" s="29" t="s">
+      <c r="C86" t="s">
         <v>242</v>
       </c>
       <c r="D86" t="s">
@@ -8891,8 +8887,8 @@
       <c r="H86" t="n">
         <v>3.20469</v>
       </c>
-      <c r="I86" t="e">
-        <v>#N/A</v>
+      <c r="I86" t="n">
+        <v>0.015</v>
       </c>
       <c r="J86" t="e">
         <v>#N/A</v>
@@ -8900,17 +8896,17 @@
       <c r="K86" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L86" t="e">
-        <v>#N/A</v>
+      <c r="L86" t="s">
+        <v>245</v>
       </c>
       <c r="M86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O86" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P86" t="e">
         <v>#N/A</v>
@@ -8940,17 +8936,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y86" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="87" ht="19" customHeight="1">
       <c r="A87" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B87" t="s">
         <v>241</v>
       </c>
-      <c r="C87" s="29" t="s">
+      <c r="C87" t="s">
         <v>242</v>
       </c>
       <c r="D87" t="s">
@@ -8968,8 +8964,8 @@
       <c r="H87" t="n">
         <v>3.2053</v>
       </c>
-      <c r="I87" t="e">
-        <v>#N/A</v>
+      <c r="I87" t="n">
+        <v>0.015</v>
       </c>
       <c r="J87" t="e">
         <v>#N/A</v>
@@ -8977,17 +8973,17 @@
       <c r="K87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L87" t="e">
-        <v>#N/A</v>
+      <c r="L87" t="s">
+        <v>245</v>
       </c>
       <c r="M87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N87" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O87" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P87" t="e">
         <v>#N/A</v>
@@ -9017,17 +9013,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y87" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
       <c r="A88" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B88" t="s">
         <v>241</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" t="s">
         <v>242</v>
       </c>
       <c r="D88" t="s">
@@ -9045,8 +9041,8 @@
       <c r="H88" t="n">
         <v>3.20831</v>
       </c>
-      <c r="I88" t="e">
-        <v>#N/A</v>
+      <c r="I88" t="n">
+        <v>0.015</v>
       </c>
       <c r="J88" t="e">
         <v>#N/A</v>
@@ -9054,17 +9050,17 @@
       <c r="K88" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L88" t="e">
-        <v>#N/A</v>
+      <c r="L88" t="s">
+        <v>245</v>
       </c>
       <c r="M88" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N88" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O88" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P88" t="e">
         <v>#N/A</v>
@@ -9094,17 +9090,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y88" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
       <c r="A89" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B89" t="s">
         <v>241</v>
       </c>
-      <c r="C89" s="29" t="s">
+      <c r="C89" t="s">
         <v>242</v>
       </c>
       <c r="D89" t="s">
@@ -9122,8 +9118,8 @@
       <c r="H89" t="n">
         <v>3.21102</v>
       </c>
-      <c r="I89" t="e">
-        <v>#N/A</v>
+      <c r="I89" t="n">
+        <v>0.015</v>
       </c>
       <c r="J89" t="e">
         <v>#N/A</v>
@@ -9131,17 +9127,17 @@
       <c r="K89" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L89" t="e">
-        <v>#N/A</v>
+      <c r="L89" t="s">
+        <v>245</v>
       </c>
       <c r="M89" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N89" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O89" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P89" t="e">
         <v>#N/A</v>
@@ -9171,17 +9167,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y89" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
       <c r="A90" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B90" t="s">
         <v>241</v>
       </c>
-      <c r="C90" s="29" t="s">
+      <c r="C90" t="s">
         <v>242</v>
       </c>
       <c r="D90" t="s">
@@ -9199,8 +9195,8 @@
       <c r="H90" t="n">
         <v>3.21614</v>
       </c>
-      <c r="I90" t="e">
-        <v>#N/A</v>
+      <c r="I90" t="n">
+        <v>0.015</v>
       </c>
       <c r="J90" t="e">
         <v>#N/A</v>
@@ -9208,17 +9204,17 @@
       <c r="K90" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L90" t="e">
-        <v>#N/A</v>
+      <c r="L90" t="s">
+        <v>245</v>
       </c>
       <c r="M90" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N90" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O90" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P90" t="e">
         <v>#N/A</v>
@@ -9248,17 +9244,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y90" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="91" ht="19" customHeight="1">
       <c r="A91" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B91" t="s">
         <v>241</v>
       </c>
-      <c r="C91" s="29" t="s">
+      <c r="C91" t="s">
         <v>242</v>
       </c>
       <c r="D91" t="s">
@@ -9276,8 +9272,8 @@
       <c r="H91" t="n">
         <v>3.21795</v>
       </c>
-      <c r="I91" t="e">
-        <v>#N/A</v>
+      <c r="I91" t="n">
+        <v>0.015</v>
       </c>
       <c r="J91" t="e">
         <v>#N/A</v>
@@ -9285,17 +9281,17 @@
       <c r="K91" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L91" t="e">
-        <v>#N/A</v>
+      <c r="L91" t="s">
+        <v>245</v>
       </c>
       <c r="M91" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N91" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O91" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P91" t="e">
         <v>#N/A</v>
@@ -9325,17 +9321,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y91" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
       <c r="A92" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B92" t="s">
         <v>241</v>
       </c>
-      <c r="C92" s="29" t="s">
+      <c r="C92" t="s">
         <v>242</v>
       </c>
       <c r="D92" t="s">
@@ -9353,8 +9349,8 @@
       <c r="H92" t="n">
         <v>3.22006</v>
       </c>
-      <c r="I92" t="e">
-        <v>#N/A</v>
+      <c r="I92" t="n">
+        <v>0.015</v>
       </c>
       <c r="J92" t="e">
         <v>#N/A</v>
@@ -9362,17 +9358,17 @@
       <c r="K92" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L92" t="e">
-        <v>#N/A</v>
+      <c r="L92" t="s">
+        <v>245</v>
       </c>
       <c r="M92" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N92" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P92" t="e">
         <v>#N/A</v>
@@ -9402,17 +9398,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y92" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="93" ht="19" customHeight="1">
       <c r="A93" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B93" t="s">
         <v>241</v>
       </c>
-      <c r="C93" s="29" t="s">
+      <c r="C93" t="s">
         <v>242</v>
       </c>
       <c r="D93" t="s">
@@ -9430,8 +9426,8 @@
       <c r="H93" t="n">
         <v>3.22067</v>
       </c>
-      <c r="I93" t="e">
-        <v>#N/A</v>
+      <c r="I93" t="n">
+        <v>0.015</v>
       </c>
       <c r="J93" t="e">
         <v>#N/A</v>
@@ -9439,17 +9435,17 @@
       <c r="K93" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L93" t="e">
-        <v>#N/A</v>
+      <c r="L93" t="s">
+        <v>245</v>
       </c>
       <c r="M93" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N93" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O93" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P93" t="e">
         <v>#N/A</v>
@@ -9479,17 +9475,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y93" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
       <c r="A94" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B94" t="s">
         <v>241</v>
       </c>
-      <c r="C94" s="29" t="s">
+      <c r="C94" t="s">
         <v>242</v>
       </c>
       <c r="D94" t="s">
@@ -9507,8 +9503,8 @@
       <c r="H94" t="n">
         <v>3.22308</v>
       </c>
-      <c r="I94" t="e">
-        <v>#N/A</v>
+      <c r="I94" t="n">
+        <v>0.015</v>
       </c>
       <c r="J94" t="e">
         <v>#N/A</v>
@@ -9516,17 +9512,17 @@
       <c r="K94" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L94" t="e">
-        <v>#N/A</v>
+      <c r="L94" t="s">
+        <v>245</v>
       </c>
       <c r="M94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N94" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O94" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P94" t="e">
         <v>#N/A</v>
@@ -9556,17 +9552,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y94" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="95" ht="19" customHeight="1">
       <c r="A95" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B95" t="s">
         <v>241</v>
       </c>
-      <c r="C95" s="29" t="s">
+      <c r="C95" t="s">
         <v>242</v>
       </c>
       <c r="D95" t="s">
@@ -9584,8 +9580,8 @@
       <c r="H95" t="n">
         <v>3.22398</v>
       </c>
-      <c r="I95" t="e">
-        <v>#N/A</v>
+      <c r="I95" t="n">
+        <v>0.015</v>
       </c>
       <c r="J95" t="e">
         <v>#N/A</v>
@@ -9593,17 +9589,17 @@
       <c r="K95" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L95" t="e">
-        <v>#N/A</v>
+      <c r="L95" t="s">
+        <v>245</v>
       </c>
       <c r="M95" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N95" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O95" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P95" t="e">
         <v>#N/A</v>
@@ -9633,17 +9629,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y95" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" ht="19" customHeight="1">
       <c r="A96" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B96" t="s">
         <v>241</v>
       </c>
-      <c r="C96" s="29" t="s">
+      <c r="C96" t="s">
         <v>242</v>
       </c>
       <c r="D96" t="s">
@@ -9661,8 +9657,8 @@
       <c r="H96" t="n">
         <v>3.23061</v>
       </c>
-      <c r="I96" t="e">
-        <v>#N/A</v>
+      <c r="I96" t="n">
+        <v>0.015</v>
       </c>
       <c r="J96" t="e">
         <v>#N/A</v>
@@ -9670,17 +9666,17 @@
       <c r="K96" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L96" t="e">
-        <v>#N/A</v>
+      <c r="L96" t="s">
+        <v>245</v>
       </c>
       <c r="M96" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N96" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O96" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P96" t="e">
         <v>#N/A</v>
@@ -9710,17 +9706,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y96" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
       <c r="A97" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B97" t="s">
         <v>241</v>
       </c>
-      <c r="C97" s="29" t="s">
+      <c r="C97" t="s">
         <v>242</v>
       </c>
       <c r="D97" t="s">
@@ -9738,8 +9734,8 @@
       <c r="H97" t="n">
         <v>3.23302</v>
       </c>
-      <c r="I97" t="e">
-        <v>#N/A</v>
+      <c r="I97" t="n">
+        <v>0.015</v>
       </c>
       <c r="J97" t="e">
         <v>#N/A</v>
@@ -9747,17 +9743,17 @@
       <c r="K97" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L97" t="e">
-        <v>#N/A</v>
+      <c r="L97" t="s">
+        <v>245</v>
       </c>
       <c r="M97" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N97" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O97" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P97" t="e">
         <v>#N/A</v>
@@ -9787,17 +9783,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y97" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" ht="19" customHeight="1">
       <c r="A98" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B98" t="s">
         <v>241</v>
       </c>
-      <c r="C98" s="29" t="s">
+      <c r="C98" t="s">
         <v>242</v>
       </c>
       <c r="D98" t="s">
@@ -9815,8 +9811,8 @@
       <c r="H98" t="n">
         <v>3.23513</v>
       </c>
-      <c r="I98" t="e">
-        <v>#N/A</v>
+      <c r="I98" t="n">
+        <v>0.015</v>
       </c>
       <c r="J98" t="e">
         <v>#N/A</v>
@@ -9824,17 +9820,17 @@
       <c r="K98" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L98" t="e">
-        <v>#N/A</v>
+      <c r="L98" t="s">
+        <v>245</v>
       </c>
       <c r="M98" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N98" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O98" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P98" t="e">
         <v>#N/A</v>
@@ -9864,17 +9860,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y98" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="99" ht="19" customHeight="1">
       <c r="A99" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B99" t="s">
         <v>241</v>
       </c>
-      <c r="C99" s="29" t="s">
+      <c r="C99" t="s">
         <v>242</v>
       </c>
       <c r="D99" t="s">
@@ -9892,8 +9888,8 @@
       <c r="H99" t="n">
         <v>3.23604</v>
       </c>
-      <c r="I99" t="e">
-        <v>#N/A</v>
+      <c r="I99" t="n">
+        <v>0.015</v>
       </c>
       <c r="J99" t="e">
         <v>#N/A</v>
@@ -9901,17 +9897,17 @@
       <c r="K99" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L99" t="e">
-        <v>#N/A</v>
+      <c r="L99" t="s">
+        <v>245</v>
       </c>
       <c r="M99" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N99" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O99" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P99" t="e">
         <v>#N/A</v>
@@ -9941,17 +9937,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y99" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" ht="19" customHeight="1">
       <c r="A100" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B100" t="s">
         <v>241</v>
       </c>
-      <c r="C100" s="29" t="s">
+      <c r="C100" t="s">
         <v>242</v>
       </c>
       <c r="D100" t="s">
@@ -9969,8 +9965,8 @@
       <c r="H100" t="n">
         <v>3.24782</v>
       </c>
-      <c r="I100" t="e">
-        <v>#N/A</v>
+      <c r="I100" t="n">
+        <v>0.015</v>
       </c>
       <c r="J100" t="e">
         <v>#N/A</v>
@@ -9978,17 +9974,17 @@
       <c r="K100" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L100" t="e">
-        <v>#N/A</v>
+      <c r="L100" t="s">
+        <v>245</v>
       </c>
       <c r="M100" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N100" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O100" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P100" t="e">
         <v>#N/A</v>
@@ -10018,17 +10014,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y100" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="101" ht="19" customHeight="1">
       <c r="A101" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B101" t="s">
         <v>241</v>
       </c>
-      <c r="C101" s="29" t="s">
+      <c r="C101" t="s">
         <v>242</v>
       </c>
       <c r="D101" t="s">
@@ -10046,8 +10042,8 @@
       <c r="H101" t="n">
         <v>3.25214</v>
       </c>
-      <c r="I101" t="e">
-        <v>#N/A</v>
+      <c r="I101" t="n">
+        <v>0.015</v>
       </c>
       <c r="J101" t="e">
         <v>#N/A</v>
@@ -10055,17 +10051,17 @@
       <c r="K101" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L101" t="e">
-        <v>#N/A</v>
+      <c r="L101" t="s">
+        <v>245</v>
       </c>
       <c r="M101" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N101" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O101" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P101" t="e">
         <v>#N/A</v>
@@ -10095,17 +10091,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y101" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" ht="19" customHeight="1">
       <c r="A102" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B102" t="s">
         <v>241</v>
       </c>
-      <c r="C102" s="29" t="s">
+      <c r="C102" t="s">
         <v>242</v>
       </c>
       <c r="D102" t="s">
@@ -10123,8 +10119,8 @@
       <c r="H102" t="n">
         <v>3.25413</v>
       </c>
-      <c r="I102" t="e">
-        <v>#N/A</v>
+      <c r="I102" t="n">
+        <v>0.015</v>
       </c>
       <c r="J102" t="e">
         <v>#N/A</v>
@@ -10132,17 +10128,17 @@
       <c r="K102" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L102" t="e">
-        <v>#N/A</v>
+      <c r="L102" t="s">
+        <v>245</v>
       </c>
       <c r="M102" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N102" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O102" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P102" t="e">
         <v>#N/A</v>
@@ -10172,17 +10168,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y102" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="103" ht="19" customHeight="1">
       <c r="A103" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B103" t="s">
         <v>241</v>
       </c>
-      <c r="C103" s="29" t="s">
+      <c r="C103" t="s">
         <v>242</v>
       </c>
       <c r="D103" t="s">
@@ -10200,8 +10196,8 @@
       <c r="H103" t="n">
         <v>3.26077</v>
       </c>
-      <c r="I103" t="e">
-        <v>#N/A</v>
+      <c r="I103" t="n">
+        <v>0.015</v>
       </c>
       <c r="J103" t="e">
         <v>#N/A</v>
@@ -10209,17 +10205,17 @@
       <c r="K103" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L103" t="e">
-        <v>#N/A</v>
+      <c r="L103" t="s">
+        <v>245</v>
       </c>
       <c r="M103" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N103" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O103" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P103" t="e">
         <v>#N/A</v>
@@ -10249,17 +10245,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y103" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="104" ht="19" customHeight="1">
       <c r="A104" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B104" t="s">
         <v>241</v>
       </c>
-      <c r="C104" s="29" t="s">
+      <c r="C104" t="s">
         <v>242</v>
       </c>
       <c r="D104" t="s">
@@ -10277,8 +10273,8 @@
       <c r="H104" t="n">
         <v>3.26807</v>
       </c>
-      <c r="I104" t="e">
-        <v>#N/A</v>
+      <c r="I104" t="n">
+        <v>0.015</v>
       </c>
       <c r="J104" t="e">
         <v>#N/A</v>
@@ -10286,17 +10282,17 @@
       <c r="K104" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L104" t="e">
-        <v>#N/A</v>
+      <c r="L104" t="s">
+        <v>245</v>
       </c>
       <c r="M104" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N104" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O104" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P104" t="e">
         <v>#N/A</v>
@@ -10326,17 +10322,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y104" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
       <c r="A105" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B105" t="s">
         <v>241</v>
       </c>
-      <c r="C105" s="29" t="s">
+      <c r="C105" t="s">
         <v>242</v>
       </c>
       <c r="D105" t="s">
@@ -10354,8 +10350,8 @@
       <c r="H105" t="n">
         <v>3.27206</v>
       </c>
-      <c r="I105" t="e">
-        <v>#N/A</v>
+      <c r="I105" t="n">
+        <v>0.015</v>
       </c>
       <c r="J105" t="e">
         <v>#N/A</v>
@@ -10363,17 +10359,17 @@
       <c r="K105" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L105" t="e">
-        <v>#N/A</v>
+      <c r="L105" t="s">
+        <v>245</v>
       </c>
       <c r="M105" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N105" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O105" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P105" t="e">
         <v>#N/A</v>
@@ -10403,17 +10399,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y105" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B106" t="s">
         <v>241</v>
       </c>
-      <c r="C106" s="29" t="s">
+      <c r="C106" t="s">
         <v>242</v>
       </c>
       <c r="D106" t="s">
@@ -10431,8 +10427,8 @@
       <c r="H106" t="n">
         <v>3.2787</v>
       </c>
-      <c r="I106" t="e">
-        <v>#N/A</v>
+      <c r="I106" t="n">
+        <v>0.015</v>
       </c>
       <c r="J106" t="e">
         <v>#N/A</v>
@@ -10440,17 +10436,17 @@
       <c r="K106" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L106" t="e">
-        <v>#N/A</v>
+      <c r="L106" t="s">
+        <v>245</v>
       </c>
       <c r="M106" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N106" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O106" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P106" t="e">
         <v>#N/A</v>
@@ -10480,17 +10476,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y106" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s">
         <v>241</v>
       </c>
-      <c r="C107" s="29" t="s">
+      <c r="C107" t="s">
         <v>242</v>
       </c>
       <c r="D107" t="s">
@@ -10508,8 +10504,8 @@
       <c r="H107" t="n">
         <v>3.28667</v>
       </c>
-      <c r="I107" t="e">
-        <v>#N/A</v>
+      <c r="I107" t="n">
+        <v>0.015</v>
       </c>
       <c r="J107" t="e">
         <v>#N/A</v>
@@ -10517,17 +10513,17 @@
       <c r="K107" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L107" t="e">
-        <v>#N/A</v>
+      <c r="L107" t="s">
+        <v>245</v>
       </c>
       <c r="M107" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N107" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O107" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P107" t="e">
         <v>#N/A</v>
@@ -10557,17 +10553,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y107" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B108" t="s">
         <v>241</v>
       </c>
-      <c r="C108" s="29" t="s">
+      <c r="C108" t="s">
         <v>242</v>
       </c>
       <c r="D108" t="s">
@@ -10585,8 +10581,8 @@
       <c r="H108" t="n">
         <v>3.29024</v>
       </c>
-      <c r="I108" t="e">
-        <v>#N/A</v>
+      <c r="I108" t="n">
+        <v>0.015</v>
       </c>
       <c r="J108" t="e">
         <v>#N/A</v>
@@ -10594,17 +10590,17 @@
       <c r="K108" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L108" t="e">
-        <v>#N/A</v>
+      <c r="L108" t="s">
+        <v>245</v>
       </c>
       <c r="M108" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N108" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O108" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P108" t="e">
         <v>#N/A</v>
@@ -10634,17 +10630,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y108" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B109" t="s">
         <v>241</v>
       </c>
-      <c r="C109" s="29" t="s">
+      <c r="C109" t="s">
         <v>242</v>
       </c>
       <c r="D109" t="s">
@@ -10662,8 +10658,8 @@
       <c r="H109" t="n">
         <v>3.29311</v>
       </c>
-      <c r="I109" t="e">
-        <v>#N/A</v>
+      <c r="I109" t="n">
+        <v>0.015</v>
       </c>
       <c r="J109" t="e">
         <v>#N/A</v>
@@ -10671,17 +10667,17 @@
       <c r="K109" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L109" t="e">
-        <v>#N/A</v>
+      <c r="L109" t="s">
+        <v>245</v>
       </c>
       <c r="M109" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N109" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O109" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P109" t="e">
         <v>#N/A</v>
@@ -10711,17 +10707,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y109" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B110" t="s">
         <v>241</v>
       </c>
-      <c r="C110" s="29" t="s">
+      <c r="C110" t="s">
         <v>242</v>
       </c>
       <c r="D110" t="s">
@@ -10739,8 +10735,8 @@
       <c r="H110" t="n">
         <v>3.29643</v>
       </c>
-      <c r="I110" t="e">
-        <v>#N/A</v>
+      <c r="I110" t="n">
+        <v>0.015</v>
       </c>
       <c r="J110" t="e">
         <v>#N/A</v>
@@ -10748,17 +10744,17 @@
       <c r="K110" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L110" t="e">
-        <v>#N/A</v>
+      <c r="L110" t="s">
+        <v>245</v>
       </c>
       <c r="M110" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N110" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O110" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P110" t="e">
         <v>#N/A</v>
@@ -10788,17 +10784,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y110" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B111" t="s">
         <v>241</v>
       </c>
-      <c r="C111" s="29" t="s">
+      <c r="C111" t="s">
         <v>242</v>
       </c>
       <c r="D111" t="s">
@@ -10816,8 +10812,8 @@
       <c r="H111" t="n">
         <v>3.29945</v>
       </c>
-      <c r="I111" t="e">
-        <v>#N/A</v>
+      <c r="I111" t="n">
+        <v>0.015</v>
       </c>
       <c r="J111" t="e">
         <v>#N/A</v>
@@ -10825,17 +10821,17 @@
       <c r="K111" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L111" t="e">
-        <v>#N/A</v>
+      <c r="L111" t="s">
+        <v>245</v>
       </c>
       <c r="M111" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N111" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O111" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P111" t="e">
         <v>#N/A</v>
@@ -10865,17 +10861,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y111" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B112" t="s">
         <v>241</v>
       </c>
-      <c r="C112" s="29" t="s">
+      <c r="C112" t="s">
         <v>242</v>
       </c>
       <c r="D112" t="s">
@@ -10893,8 +10889,8 @@
       <c r="H112" t="n">
         <v>3.30261</v>
       </c>
-      <c r="I112" t="e">
-        <v>#N/A</v>
+      <c r="I112" t="n">
+        <v>0.015</v>
       </c>
       <c r="J112" t="e">
         <v>#N/A</v>
@@ -10902,17 +10898,17 @@
       <c r="K112" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L112" t="e">
-        <v>#N/A</v>
+      <c r="L112" t="s">
+        <v>245</v>
       </c>
       <c r="M112" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N112" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O112" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P112" t="e">
         <v>#N/A</v>
@@ -10942,17 +10938,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y112" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B113" t="s">
         <v>241</v>
       </c>
-      <c r="C113" s="29" t="s">
+      <c r="C113" t="s">
         <v>242</v>
       </c>
       <c r="D113" t="s">
@@ -10970,8 +10966,8 @@
       <c r="H113" t="n">
         <v>3.30412</v>
       </c>
-      <c r="I113" t="e">
-        <v>#N/A</v>
+      <c r="I113" t="n">
+        <v>0.015</v>
       </c>
       <c r="J113" t="e">
         <v>#N/A</v>
@@ -10979,17 +10975,17 @@
       <c r="K113" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L113" t="e">
-        <v>#N/A</v>
+      <c r="L113" t="s">
+        <v>245</v>
       </c>
       <c r="M113" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N113" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O113" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P113" t="e">
         <v>#N/A</v>
@@ -11019,17 +11015,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y113" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B114" t="s">
         <v>241</v>
       </c>
-      <c r="C114" s="29" t="s">
+      <c r="C114" t="s">
         <v>242</v>
       </c>
       <c r="D114" t="s">
@@ -11047,8 +11043,8 @@
       <c r="H114" t="n">
         <v>3.31076</v>
       </c>
-      <c r="I114" t="e">
-        <v>#N/A</v>
+      <c r="I114" t="n">
+        <v>0.015</v>
       </c>
       <c r="J114" t="e">
         <v>#N/A</v>
@@ -11056,17 +11052,17 @@
       <c r="K114" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L114" t="e">
-        <v>#N/A</v>
+      <c r="L114" t="s">
+        <v>245</v>
       </c>
       <c r="M114" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N114" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O114" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P114" t="e">
         <v>#N/A</v>
@@ -11096,17 +11092,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y114" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B115" t="s">
         <v>241</v>
       </c>
-      <c r="C115" s="29" t="s">
+      <c r="C115" t="s">
         <v>242</v>
       </c>
       <c r="D115" t="s">
@@ -11124,8 +11120,8 @@
       <c r="H115" t="n">
         <v>3.3146</v>
       </c>
-      <c r="I115" t="e">
-        <v>#N/A</v>
+      <c r="I115" t="n">
+        <v>0.015</v>
       </c>
       <c r="J115" t="e">
         <v>#N/A</v>
@@ -11133,17 +11129,17 @@
       <c r="K115" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L115" t="e">
-        <v>#N/A</v>
+      <c r="L115" t="s">
+        <v>245</v>
       </c>
       <c r="M115" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N115" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O115" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P115" t="e">
         <v>#N/A</v>
@@ -11173,17 +11169,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y115" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B116" t="s">
         <v>241</v>
       </c>
-      <c r="C116" s="29" t="s">
+      <c r="C116" t="s">
         <v>242</v>
       </c>
       <c r="D116" t="s">
@@ -11201,8 +11197,8 @@
       <c r="H116" t="n">
         <v>3.31752</v>
       </c>
-      <c r="I116" t="e">
-        <v>#N/A</v>
+      <c r="I116" t="n">
+        <v>0.015</v>
       </c>
       <c r="J116" t="e">
         <v>#N/A</v>
@@ -11210,17 +11206,17 @@
       <c r="K116" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L116" t="e">
-        <v>#N/A</v>
+      <c r="L116" t="s">
+        <v>245</v>
       </c>
       <c r="M116" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N116" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O116" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P116" t="e">
         <v>#N/A</v>
@@ -11250,17 +11246,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y116" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B117" t="s">
         <v>241</v>
       </c>
-      <c r="C117" s="29" t="s">
+      <c r="C117" t="s">
         <v>242</v>
       </c>
       <c r="D117" t="s">
@@ -11278,8 +11274,8 @@
       <c r="H117" t="n">
         <v>3.3203</v>
       </c>
-      <c r="I117" t="e">
-        <v>#N/A</v>
+      <c r="I117" t="n">
+        <v>0.015</v>
       </c>
       <c r="J117" t="e">
         <v>#N/A</v>
@@ -11287,17 +11283,17 @@
       <c r="K117" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L117" t="e">
-        <v>#N/A</v>
+      <c r="L117" t="s">
+        <v>245</v>
       </c>
       <c r="M117" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N117" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O117" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P117" t="e">
         <v>#N/A</v>
@@ -11327,17 +11323,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y117" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B118" t="s">
         <v>241</v>
       </c>
-      <c r="C118" s="29" t="s">
+      <c r="C118" t="s">
         <v>242</v>
       </c>
       <c r="D118" t="s">
@@ -11355,8 +11351,8 @@
       <c r="H118" t="n">
         <v>3.32322</v>
       </c>
-      <c r="I118" t="e">
-        <v>#N/A</v>
+      <c r="I118" t="n">
+        <v>0.015</v>
       </c>
       <c r="J118" t="e">
         <v>#N/A</v>
@@ -11364,17 +11360,17 @@
       <c r="K118" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L118" t="e">
-        <v>#N/A</v>
+      <c r="L118" t="s">
+        <v>245</v>
       </c>
       <c r="M118" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N118" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O118" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P118" t="e">
         <v>#N/A</v>
@@ -11404,17 +11400,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y118" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B119" t="s">
         <v>241</v>
       </c>
-      <c r="C119" s="29" t="s">
+      <c r="C119" t="s">
         <v>242</v>
       </c>
       <c r="D119" t="s">
@@ -11432,8 +11428,8 @@
       <c r="H119" t="n">
         <v>3.32614</v>
       </c>
-      <c r="I119" t="e">
-        <v>#N/A</v>
+      <c r="I119" t="n">
+        <v>0.015</v>
       </c>
       <c r="J119" t="e">
         <v>#N/A</v>
@@ -11441,17 +11437,17 @@
       <c r="K119" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L119" t="e">
-        <v>#N/A</v>
+      <c r="L119" t="s">
+        <v>245</v>
       </c>
       <c r="M119" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N119" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O119" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P119" t="e">
         <v>#N/A</v>
@@ -11481,17 +11477,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y119" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B120" t="s">
         <v>241</v>
       </c>
-      <c r="C120" s="29" t="s">
+      <c r="C120" t="s">
         <v>242</v>
       </c>
       <c r="D120" t="s">
@@ -11509,8 +11505,8 @@
       <c r="H120" t="n">
         <v>3.3292</v>
       </c>
-      <c r="I120" t="e">
-        <v>#N/A</v>
+      <c r="I120" t="n">
+        <v>0.015</v>
       </c>
       <c r="J120" t="e">
         <v>#N/A</v>
@@ -11518,17 +11514,17 @@
       <c r="K120" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L120" t="e">
-        <v>#N/A</v>
+      <c r="L120" t="s">
+        <v>245</v>
       </c>
       <c r="M120" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N120" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O120" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P120" t="e">
         <v>#N/A</v>
@@ -11558,17 +11554,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y120" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B121" t="s">
         <v>241</v>
       </c>
-      <c r="C121" s="29" t="s">
+      <c r="C121" t="s">
         <v>242</v>
       </c>
       <c r="D121" t="s">
@@ -11586,8 +11582,8 @@
       <c r="H121" t="n">
         <v>3.33213</v>
       </c>
-      <c r="I121" t="e">
-        <v>#N/A</v>
+      <c r="I121" t="n">
+        <v>0.015</v>
       </c>
       <c r="J121" t="e">
         <v>#N/A</v>
@@ -11595,17 +11591,17 @@
       <c r="K121" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L121" t="e">
-        <v>#N/A</v>
+      <c r="L121" t="s">
+        <v>245</v>
       </c>
       <c r="M121" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N121" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O121" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P121" t="e">
         <v>#N/A</v>
@@ -11635,17 +11631,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B122" t="s">
         <v>241</v>
       </c>
-      <c r="C122" s="29" t="s">
+      <c r="C122" t="s">
         <v>242</v>
       </c>
       <c r="D122" t="s">
@@ -11663,8 +11659,8 @@
       <c r="H122" t="n">
         <v>2.019288</v>
       </c>
-      <c r="I122" t="e">
-        <v>#N/A</v>
+      <c r="I122" t="n">
+        <v>0.006</v>
       </c>
       <c r="J122" t="e">
         <v>#N/A</v>
@@ -11672,17 +11668,17 @@
       <c r="K122" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L122" t="e">
-        <v>#N/A</v>
+      <c r="L122" t="s">
+        <v>245</v>
       </c>
       <c r="M122" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N122" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O122" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P122" t="e">
         <v>#N/A</v>
@@ -11712,17 +11708,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y122" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B123" t="s">
         <v>241</v>
       </c>
-      <c r="C123" s="29" t="s">
+      <c r="C123" t="s">
         <v>242</v>
       </c>
       <c r="D123" t="s">
@@ -11740,8 +11736,8 @@
       <c r="H123" t="n">
         <v>2.941223</v>
       </c>
-      <c r="I123" t="e">
-        <v>#N/A</v>
+      <c r="I123" t="n">
+        <v>0.006</v>
       </c>
       <c r="J123" t="e">
         <v>#N/A</v>
@@ -11749,17 +11745,17 @@
       <c r="K123" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L123" t="e">
-        <v>#N/A</v>
+      <c r="L123" t="s">
+        <v>245</v>
       </c>
       <c r="M123" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N123" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O123" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P123" t="e">
         <v>#N/A</v>
@@ -11789,17 +11785,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y123" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B124" t="s">
         <v>241</v>
       </c>
-      <c r="C124" s="29" t="s">
+      <c r="C124" t="s">
         <v>242</v>
       </c>
       <c r="D124" t="s">
@@ -11817,8 +11813,8 @@
       <c r="H124" t="n">
         <v>3.180879089</v>
       </c>
-      <c r="I124" t="e">
-        <v>#N/A</v>
+      <c r="I124" t="n">
+        <v>0.015</v>
       </c>
       <c r="J124" t="e">
         <v>#N/A</v>
@@ -11826,17 +11822,17 @@
       <c r="K124" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L124" t="e">
-        <v>#N/A</v>
+      <c r="L124" t="s">
+        <v>245</v>
       </c>
       <c r="M124" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N124" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O124" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P124" t="e">
         <v>#N/A</v>
@@ -11866,17 +11862,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y124" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B125" t="s">
         <v>241</v>
       </c>
-      <c r="C125" s="29" t="s">
+      <c r="C125" t="s">
         <v>242</v>
       </c>
       <c r="D125" t="s">
@@ -11894,8 +11890,8 @@
       <c r="H125" t="n">
         <v>3.204404</v>
       </c>
-      <c r="I125" t="e">
-        <v>#N/A</v>
+      <c r="I125" t="n">
+        <v>0.015</v>
       </c>
       <c r="J125" t="e">
         <v>#N/A</v>
@@ -11903,17 +11899,17 @@
       <c r="K125" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L125" t="e">
-        <v>#N/A</v>
+      <c r="L125" t="s">
+        <v>245</v>
       </c>
       <c r="M125" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N125" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O125" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P125" t="e">
         <v>#N/A</v>
@@ -11943,17 +11939,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y125" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B126" t="s">
         <v>241</v>
       </c>
-      <c r="C126" s="29" t="s">
+      <c r="C126" t="s">
         <v>242</v>
       </c>
       <c r="D126" t="s">
@@ -11971,8 +11967,8 @@
       <c r="H126" t="n">
         <v>3.235131485</v>
       </c>
-      <c r="I126" t="e">
-        <v>#N/A</v>
+      <c r="I126" t="n">
+        <v>0.015</v>
       </c>
       <c r="J126" t="e">
         <v>#N/A</v>
@@ -11980,17 +11976,17 @@
       <c r="K126" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L126" t="e">
-        <v>#N/A</v>
+      <c r="L126" t="s">
+        <v>245</v>
       </c>
       <c r="M126" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N126" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O126" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P126" t="e">
         <v>#N/A</v>
@@ -12020,17 +12016,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B127" t="s">
         <v>241</v>
       </c>
-      <c r="C127" s="29" t="s">
+      <c r="C127" t="s">
         <v>242</v>
       </c>
       <c r="D127" t="s">
@@ -12048,8 +12044,8 @@
       <c r="H127" t="n">
         <v>4.003177</v>
       </c>
-      <c r="I127" t="e">
-        <v>#N/A</v>
+      <c r="I127" t="n">
+        <v>0.03</v>
       </c>
       <c r="J127" t="e">
         <v>#N/A</v>
@@ -12057,17 +12053,17 @@
       <c r="K127" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L127" t="e">
-        <v>#N/A</v>
+      <c r="L127" t="s">
+        <v>245</v>
       </c>
       <c r="M127" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N127" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O127" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P127" t="e">
         <v>#N/A</v>
@@ -12097,17 +12093,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y127" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B128" t="s">
         <v>241</v>
       </c>
-      <c r="C128" s="29" t="s">
+      <c r="C128" t="s">
         <v>242</v>
       </c>
       <c r="D128" t="s">
@@ -12125,8 +12121,8 @@
       <c r="H128" t="n">
         <v>4.225709</v>
       </c>
-      <c r="I128" t="e">
-        <v>#N/A</v>
+      <c r="I128" t="n">
+        <v>0.03</v>
       </c>
       <c r="J128" t="e">
         <v>#N/A</v>
@@ -12134,17 +12130,17 @@
       <c r="K128" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L128" t="e">
-        <v>#N/A</v>
+      <c r="L128" t="s">
+        <v>245</v>
       </c>
       <c r="M128" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N128" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O128" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P128" t="e">
         <v>#N/A</v>
@@ -12174,7 +12170,7 @@
         <v>#N/A</v>
       </c>
       <c r="Y128" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -12183,132 +12179,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-    <hyperlink ref="C61" r:id="rId57h"/>
-    <hyperlink ref="C62" r:id="rId58h"/>
-    <hyperlink ref="C63" r:id="rId59h"/>
-    <hyperlink ref="C64" r:id="rId60h"/>
-    <hyperlink ref="C65" r:id="rId61h"/>
-    <hyperlink ref="C66" r:id="rId62h"/>
-    <hyperlink ref="C67" r:id="rId63h"/>
-    <hyperlink ref="C68" r:id="rId64h"/>
-    <hyperlink ref="C69" r:id="rId65h"/>
-    <hyperlink ref="C70" r:id="rId66h"/>
-    <hyperlink ref="C71" r:id="rId67h"/>
-    <hyperlink ref="C72" r:id="rId68h"/>
-    <hyperlink ref="C73" r:id="rId69h"/>
-    <hyperlink ref="C74" r:id="rId70h"/>
-    <hyperlink ref="C75" r:id="rId71h"/>
-    <hyperlink ref="C76" r:id="rId72h"/>
-    <hyperlink ref="C77" r:id="rId73h"/>
-    <hyperlink ref="C78" r:id="rId74h"/>
-    <hyperlink ref="C79" r:id="rId75h"/>
-    <hyperlink ref="C80" r:id="rId76h"/>
-    <hyperlink ref="C81" r:id="rId77h"/>
-    <hyperlink ref="C82" r:id="rId78h"/>
-    <hyperlink ref="C83" r:id="rId79h"/>
-    <hyperlink ref="C84" r:id="rId80h"/>
-    <hyperlink ref="C85" r:id="rId81h"/>
-    <hyperlink ref="C86" r:id="rId82h"/>
-    <hyperlink ref="C87" r:id="rId83h"/>
-    <hyperlink ref="C88" r:id="rId84h"/>
-    <hyperlink ref="C89" r:id="rId85h"/>
-    <hyperlink ref="C90" r:id="rId86h"/>
-    <hyperlink ref="C91" r:id="rId87h"/>
-    <hyperlink ref="C92" r:id="rId88h"/>
-    <hyperlink ref="C93" r:id="rId89h"/>
-    <hyperlink ref="C94" r:id="rId90h"/>
-    <hyperlink ref="C95" r:id="rId91h"/>
-    <hyperlink ref="C96" r:id="rId92h"/>
-    <hyperlink ref="C97" r:id="rId93h"/>
-    <hyperlink ref="C98" r:id="rId94h"/>
-    <hyperlink ref="C99" r:id="rId95h"/>
-    <hyperlink ref="C100" r:id="rId96h"/>
-    <hyperlink ref="C101" r:id="rId97h"/>
-    <hyperlink ref="C102" r:id="rId98h"/>
-    <hyperlink ref="C103" r:id="rId99h"/>
-    <hyperlink ref="C104" r:id="rId100h"/>
-    <hyperlink ref="C105" r:id="rId101h"/>
-    <hyperlink ref="C106" r:id="rId102h"/>
-    <hyperlink ref="C107" r:id="rId103h"/>
-    <hyperlink ref="C108" r:id="rId104h"/>
-    <hyperlink ref="C109" r:id="rId105h"/>
-    <hyperlink ref="C110" r:id="rId106h"/>
-    <hyperlink ref="C111" r:id="rId107h"/>
-    <hyperlink ref="C112" r:id="rId108h"/>
-    <hyperlink ref="C113" r:id="rId109h"/>
-    <hyperlink ref="C114" r:id="rId110h"/>
-    <hyperlink ref="C115" r:id="rId111h"/>
-    <hyperlink ref="C116" r:id="rId112h"/>
-    <hyperlink ref="C117" r:id="rId113h"/>
-    <hyperlink ref="C118" r:id="rId114h"/>
-    <hyperlink ref="C119" r:id="rId115h"/>
-    <hyperlink ref="C120" r:id="rId116h"/>
-    <hyperlink ref="C121" r:id="rId117h"/>
-    <hyperlink ref="C122" r:id="rId118h"/>
-    <hyperlink ref="C123" r:id="rId119h"/>
-    <hyperlink ref="C124" r:id="rId120h"/>
-    <hyperlink ref="C125" r:id="rId121h"/>
-    <hyperlink ref="C126" r:id="rId122h"/>
-    <hyperlink ref="C127" r:id="rId123h"/>
-    <hyperlink ref="C128" r:id="rId124h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
